--- a/EGSA2025_performance.xlsx
+++ b/EGSA2025_performance.xlsx
@@ -19,36 +19,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="10">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>loan_freq</t>
-  </si>
-  <si>
-    <t>total_interest_amount</t>
-  </si>
-  <si>
-    <t>monthly_payment</t>
-  </si>
-  <si>
-    <t>achievement</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+  <si>
+    <t>business_date</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Q1_plan</t>
+  </si>
+  <si>
+    <t>Q1_achievement</t>
+  </si>
+  <si>
+    <t>Monthly_payment_Q3</t>
+  </si>
+  <si>
+    <t>Q2_plan</t>
+  </si>
+  <si>
+    <t>Q2_achievement</t>
+  </si>
+  <si>
+    <t>fee_charge</t>
   </si>
   <si>
     <t>volentary_saving</t>
   </si>
   <si>
-    <t>fee_charge</t>
-  </si>
-  <si>
     <t>Benefit_gain</t>
   </si>
   <si>
-    <t>no_new_members_by</t>
-  </si>
-  <si>
-    <t>NULL</t>
+    <t>Expenditure</t>
+  </si>
+  <si>
+    <t>total_payr</t>
+  </si>
+  <si>
+    <t>Geetu Bekela</t>
+  </si>
+  <si>
+    <t>Walfana Megersa</t>
+  </si>
+  <si>
+    <t>Fayisa Badhu</t>
+  </si>
+  <si>
+    <t>Silash Dabesa</t>
+  </si>
+  <si>
+    <t>Warkitu Dilba</t>
+  </si>
+  <si>
+    <t>Kenanisa Bikila</t>
+  </si>
+  <si>
+    <t>Lalise Megersa</t>
+  </si>
+  <si>
+    <t>Lami Diro</t>
+  </si>
+  <si>
+    <t>Boki Bayena</t>
+  </si>
+  <si>
+    <t>Salamon Zarihun</t>
+  </si>
+  <si>
+    <t>Warki Lemma</t>
+  </si>
+  <si>
+    <t>Dajane Guta</t>
+  </si>
+  <si>
+    <t>Jabeessaa Dhugumaa</t>
+  </si>
+  <si>
+    <t>Barsisa Merga</t>
+  </si>
+  <si>
+    <t>Abera Asefa</t>
+  </si>
+  <si>
+    <t>Alamuu Guutaa</t>
+  </si>
+  <si>
+    <t>Naggasaa Dheeressaa</t>
+  </si>
+  <si>
+    <t>Nabiyat Habtewold</t>
+  </si>
+  <si>
+    <t>Chaluma Uma</t>
+  </si>
+  <si>
+    <t>Ababa Fayisa</t>
+  </si>
+  <si>
+    <t>Worku Bekele</t>
+  </si>
+  <si>
+    <t>Milkesa Gebre</t>
+  </si>
+  <si>
+    <t>Worku Guta</t>
   </si>
 </sst>
 </file>
@@ -532,8 +610,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -855,10 +934,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -886,672 +970,960 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>45854</v>
+      </c>
+      <c r="B2">
         <v>1001</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D2">
+        <v>37500</v>
+      </c>
+      <c r="E2">
+        <v>41500</v>
+      </c>
+      <c r="F2">
         <v>5000</v>
       </c>
-      <c r="E2">
+      <c r="G2">
+        <v>70000</v>
+      </c>
+      <c r="H2">
         <v>72000</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
+      <c r="I2">
         <v>242</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>59000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>45795</v>
+      </c>
+      <c r="B3">
         <v>1002</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>17500</v>
+      <c r="C3" t="s">
+        <v>14</v>
       </c>
       <c r="D3">
+        <v>37500</v>
+      </c>
+      <c r="E3">
+        <v>41500</v>
+      </c>
+      <c r="F3">
         <v>5000</v>
       </c>
-      <c r="E3">
+      <c r="G3">
+        <v>70000</v>
+      </c>
+      <c r="H3">
         <v>132525</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
+      <c r="I3">
         <v>1400</v>
       </c>
-      <c r="H3">
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
         <v>23625</v>
       </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="L3">
+        <v>1950</v>
+      </c>
+      <c r="M3">
+        <v>53500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>45814</v>
+      </c>
+      <c r="B4">
         <v>1003</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>17250</v>
+      <c r="C4" t="s">
+        <v>15</v>
       </c>
       <c r="D4">
+        <v>37500</v>
+      </c>
+      <c r="E4">
+        <v>41500</v>
+      </c>
+      <c r="F4">
         <v>5000</v>
       </c>
-      <c r="E4">
-        <v>121500</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
+        <v>70000</v>
+      </c>
+      <c r="H4">
+        <v>135500</v>
+      </c>
+      <c r="I4">
         <v>650</v>
       </c>
-      <c r="H4">
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>15250</v>
       </c>
-      <c r="I4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>44500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>45795</v>
+      </c>
+      <c r="B5">
         <v>1004</v>
       </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D5">
+        <v>37500</v>
+      </c>
+      <c r="E5">
+        <v>41500</v>
+      </c>
+      <c r="F5">
         <v>3000</v>
       </c>
-      <c r="E5">
+      <c r="G5">
+        <v>70000</v>
+      </c>
+      <c r="H5">
         <v>44500</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>6900</v>
+      </c>
+      <c r="M5">
+        <v>43500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>45854</v>
+      </c>
+      <c r="B6">
         <v>1005</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>37500</v>
+      </c>
+      <c r="E6">
+        <v>41500</v>
+      </c>
+      <c r="F6">
+        <v>5000</v>
+      </c>
+      <c r="G6">
+        <v>70000</v>
+      </c>
+      <c r="H6">
+        <v>48500</v>
+      </c>
+      <c r="I6">
+        <v>892</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>15250</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>43500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>45795</v>
+      </c>
+      <c r="B7">
+        <v>1006</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <v>37500</v>
+      </c>
+      <c r="E7">
+        <v>41500</v>
+      </c>
+      <c r="F7">
+        <v>5000</v>
+      </c>
+      <c r="G7">
+        <v>70000</v>
+      </c>
+      <c r="H7">
+        <v>122000</v>
+      </c>
+      <c r="I7">
+        <v>650</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>15350</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>45795</v>
+      </c>
+      <c r="B8">
+        <v>1007</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>37500</v>
+      </c>
+      <c r="E8">
+        <v>41500</v>
+      </c>
+      <c r="F8">
+        <v>5000</v>
+      </c>
+      <c r="G8">
+        <v>70000</v>
+      </c>
+      <c r="H8">
+        <v>46500</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>2250</v>
       </c>
-      <c r="D6">
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>45795</v>
+      </c>
+      <c r="B9">
+        <v>1008</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>37500</v>
+      </c>
+      <c r="E9">
+        <v>41500</v>
+      </c>
+      <c r="F9">
+        <v>4000</v>
+      </c>
+      <c r="G9">
+        <v>70000</v>
+      </c>
+      <c r="H9">
+        <v>111000</v>
+      </c>
+      <c r="I9">
+        <v>650</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>15250</v>
+      </c>
+      <c r="L9">
+        <v>200</v>
+      </c>
+      <c r="M9">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>45818</v>
+      </c>
+      <c r="B10">
+        <v>1009</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10">
+        <v>37500</v>
+      </c>
+      <c r="E10">
+        <v>41500</v>
+      </c>
+      <c r="F10">
+        <v>4000</v>
+      </c>
+      <c r="G10">
+        <v>70000</v>
+      </c>
+      <c r="H10">
+        <v>46500</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>45844</v>
+      </c>
+      <c r="B11">
+        <v>1010</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11">
+        <v>37500</v>
+      </c>
+      <c r="E11">
+        <v>41500</v>
+      </c>
+      <c r="F11">
         <v>5000</v>
       </c>
-      <c r="E6">
-        <v>48500</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>892</v>
-      </c>
-      <c r="H6">
-        <v>15250</v>
-      </c>
-      <c r="I6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>1006</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>17350</v>
-      </c>
-      <c r="D7">
+      <c r="G11">
+        <v>70000</v>
+      </c>
+      <c r="H11">
+        <v>103000</v>
+      </c>
+      <c r="I11">
+        <v>4400</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>20250</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>45935</v>
+      </c>
+      <c r="B12">
+        <v>1011</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12">
+        <v>37500</v>
+      </c>
+      <c r="E12">
+        <v>41500</v>
+      </c>
+      <c r="F12">
         <v>5000</v>
       </c>
-      <c r="E7">
-        <v>122000</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>650</v>
-      </c>
-      <c r="H7">
-        <v>15350</v>
-      </c>
-      <c r="I7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1007</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8">
-        <v>6000</v>
-      </c>
-      <c r="D8">
+      <c r="G12">
+        <v>70000</v>
+      </c>
+      <c r="H12">
+        <v>46500</v>
+      </c>
+      <c r="I12">
+        <v>700</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>2250</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>45849</v>
+      </c>
+      <c r="B13">
+        <v>1012</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13">
+        <v>37500</v>
+      </c>
+      <c r="E13">
+        <v>41500</v>
+      </c>
+      <c r="F13">
         <v>5000</v>
       </c>
-      <c r="E8">
-        <v>46500</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
+      <c r="G13">
+        <v>70000</v>
+      </c>
+      <c r="H13">
+        <v>120500</v>
+      </c>
+      <c r="I13">
+        <v>200</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>5825</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>45862</v>
+      </c>
+      <c r="B14">
+        <v>1013</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14">
+        <v>37500</v>
+      </c>
+      <c r="E14">
+        <v>41500</v>
+      </c>
+      <c r="F14">
+        <v>4000</v>
+      </c>
+      <c r="G14">
+        <v>70000</v>
+      </c>
+      <c r="H14">
+        <v>83000</v>
+      </c>
+      <c r="I14">
+        <v>937</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>9250</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>45846</v>
+      </c>
+      <c r="B15">
+        <v>1014</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15">
+        <v>37500</v>
+      </c>
+      <c r="E15">
+        <v>41500</v>
+      </c>
+      <c r="F15">
+        <v>5000</v>
+      </c>
+      <c r="G15">
+        <v>70000</v>
+      </c>
+      <c r="H15">
+        <v>84000</v>
+      </c>
+      <c r="I15">
+        <v>1250</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>2500</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>45977</v>
+      </c>
+      <c r="B16">
+        <v>1015</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16">
+        <v>37500</v>
+      </c>
+      <c r="E16">
+        <v>36000</v>
+      </c>
+      <c r="F16">
+        <v>4000</v>
+      </c>
+      <c r="G16">
+        <v>70000</v>
+      </c>
+      <c r="H16">
+        <v>62000</v>
+      </c>
+      <c r="I16">
+        <v>2000</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>46000</v>
+      </c>
+      <c r="B17">
+        <v>1016</v>
+      </c>
+      <c r="C17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17">
+        <v>37500</v>
+      </c>
+      <c r="E17">
+        <v>14000</v>
+      </c>
+      <c r="F17">
+        <v>3000</v>
+      </c>
+      <c r="G17">
+        <v>70000</v>
+      </c>
+      <c r="H17">
+        <v>43000</v>
+      </c>
+      <c r="I17">
+        <v>2000</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>46004</v>
+      </c>
+      <c r="B18">
+        <v>1017</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18">
+        <v>37500</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>3000</v>
+      </c>
+      <c r="G18">
+        <v>70000</v>
+      </c>
+      <c r="H18">
+        <v>43000</v>
+      </c>
+      <c r="I18">
+        <v>2400</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>5850</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B19">
+        <v>1019</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19">
+        <v>37500</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>3000</v>
+      </c>
+      <c r="G19">
+        <v>70000</v>
+      </c>
+      <c r="H19">
+        <v>42000</v>
+      </c>
+      <c r="I19">
+        <v>2000</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B20">
+        <v>1020</v>
+      </c>
+      <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20">
+        <v>37500</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>1000</v>
+      </c>
+      <c r="G20">
+        <v>70000</v>
+      </c>
+      <c r="H20">
+        <v>11000</v>
+      </c>
+      <c r="I20">
+        <v>2000</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B21">
+        <v>1021</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21">
+        <v>37500</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>2000</v>
+      </c>
+      <c r="G21">
+        <v>70000</v>
+      </c>
+      <c r="H21">
+        <v>2000</v>
+      </c>
+      <c r="I21">
+        <v>2000</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B22">
+        <v>1022</v>
+      </c>
+      <c r="C22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22">
+        <v>37500</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>3000</v>
+      </c>
+      <c r="G22">
+        <v>70000</v>
+      </c>
+      <c r="H22">
+        <v>12000</v>
+      </c>
+      <c r="I22">
+        <v>2000</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>46052</v>
+      </c>
+      <c r="B23">
+        <v>1023</v>
+      </c>
+      <c r="C23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23">
+        <v>37500</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>3000</v>
+      </c>
+      <c r="G23">
+        <v>70000</v>
+      </c>
+      <c r="H23">
+        <v>42000</v>
+      </c>
+      <c r="I23">
+        <v>2000</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
         <v>2250</v>
       </c>
-      <c r="I8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>1008</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>2250</v>
-      </c>
-      <c r="D9">
-        <v>4000</v>
-      </c>
-      <c r="E9">
-        <v>111000</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>650</v>
-      </c>
-      <c r="H9">
-        <v>15250</v>
-      </c>
-      <c r="I9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1009</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10">
-        <v>4000</v>
-      </c>
-      <c r="E10">
-        <v>46500</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>1010</v>
-      </c>
-      <c r="B11">
-        <v>3</v>
-      </c>
-      <c r="C11">
-        <v>7000</v>
-      </c>
-      <c r="D11">
-        <v>5000</v>
-      </c>
-      <c r="E11">
-        <v>103000</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>4400</v>
-      </c>
-      <c r="H11">
-        <v>20250</v>
-      </c>
-      <c r="I11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>1011</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>6000</v>
-      </c>
-      <c r="D12">
-        <v>5000</v>
-      </c>
-      <c r="E12">
-        <v>46500</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>700</v>
-      </c>
-      <c r="H12">
-        <v>2250</v>
-      </c>
-      <c r="I12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>1012</v>
-      </c>
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13">
-        <v>5000</v>
-      </c>
-      <c r="E13">
-        <v>120500</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>200</v>
-      </c>
-      <c r="H13">
-        <v>5825</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>1013</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>2250</v>
-      </c>
-      <c r="D14">
-        <v>4000</v>
-      </c>
-      <c r="E14">
-        <v>83000</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>937</v>
-      </c>
-      <c r="H14">
-        <v>9250</v>
-      </c>
-      <c r="I14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>1014</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>2500</v>
-      </c>
-      <c r="D15">
-        <v>5000</v>
-      </c>
-      <c r="E15">
-        <v>84000</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>1250</v>
-      </c>
-      <c r="H15">
-        <v>2500</v>
-      </c>
-      <c r="I15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>1015</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16">
-        <v>4000</v>
-      </c>
-      <c r="E16">
-        <v>62000</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>46057</v>
+      </c>
+      <c r="B24">
+        <v>1024</v>
+      </c>
+      <c r="C24" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24">
+        <v>37500</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>3000</v>
+      </c>
+      <c r="G24">
+        <v>70000</v>
+      </c>
+      <c r="H24">
+        <v>99000</v>
+      </c>
+      <c r="I24">
         <v>2000</v>
       </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>1016</v>
-      </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17">
-        <v>3000</v>
-      </c>
-      <c r="E17">
-        <v>43000</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>2000</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>1017</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>2250</v>
-      </c>
-      <c r="D18">
-        <v>3000</v>
-      </c>
-      <c r="E18">
-        <v>43000</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>2400</v>
-      </c>
-      <c r="H18">
-        <v>5850</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>1019</v>
-      </c>
-      <c r="B19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19">
-        <v>3000</v>
-      </c>
-      <c r="E19">
-        <v>42000</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>2000</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>1020</v>
-      </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20">
-        <v>1000</v>
-      </c>
-      <c r="E20">
-        <v>11000</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>2000</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>1021</v>
-      </c>
-      <c r="B21" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21">
-        <v>2000</v>
-      </c>
-      <c r="E21">
-        <v>2000</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>2000</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>1022</v>
-      </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22">
-        <v>3000</v>
-      </c>
-      <c r="E22">
-        <v>12000</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>2000</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>1023</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
-        <v>2250</v>
-      </c>
-      <c r="D23">
-        <v>3000</v>
-      </c>
-      <c r="E23">
-        <v>42000</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>2000</v>
-      </c>
-      <c r="H23">
-        <v>2250</v>
-      </c>
-      <c r="I23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>1024</v>
-      </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24">
-        <v>3000</v>
-      </c>
-      <c r="E24">
-        <v>99000</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>2000</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24" t="s">
-        <v>9</v>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2025_performance.xlsx
+++ b/EGSA2025_performance.xlsx
@@ -33,9 +33,6 @@
     <t>Q1_plan</t>
   </si>
   <si>
-    <t>Q1_achievement</t>
-  </si>
-  <si>
     <t>Monthly_payment_Q3</t>
   </si>
   <si>
@@ -127,6 +124,9 @@
   </si>
   <si>
     <t>Worku Guta</t>
+  </si>
+  <si>
+    <t>achievement</t>
   </si>
 </sst>
 </file>
@@ -956,31 +956,31 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -991,7 +991,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1032,7 +1032,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1073,7 +1073,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1114,7 +1114,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1155,7 +1155,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1196,7 +1196,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1237,7 +1237,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1278,7 +1278,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1319,7 +1319,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1360,7 +1360,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1401,7 +1401,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1442,7 +1442,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1483,7 +1483,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1524,7 +1524,7 @@
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1565,7 +1565,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1606,7 +1606,7 @@
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1647,7 +1647,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1688,7 +1688,7 @@
         <v>1019</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1729,7 +1729,7 @@
         <v>1020</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1770,7 +1770,7 @@
         <v>1021</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1811,7 +1811,7 @@
         <v>1022</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1852,7 +1852,7 @@
         <v>1023</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1893,7 +1893,7 @@
         <v>1024</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <v>37500</v>

--- a/EGSA2025_performance.xlsx
+++ b/EGSA2025_performance.xlsx
@@ -857,13 +857,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.21875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -908,7 +901,8 @@
         <v>5000</v>
       </c>
       <c r="E2">
-        <v>72000</v>
+        <f>73000+1000</f>
+        <v>74000</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -937,7 +931,8 @@
         <v>5000</v>
       </c>
       <c r="E3">
-        <v>132525</v>
+        <f>133525+1000</f>
+        <v>134525</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -966,7 +961,8 @@
         <v>5000</v>
       </c>
       <c r="E4">
-        <v>135500</v>
+        <f>136500+1000</f>
+        <v>137500</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -995,7 +991,8 @@
         <v>3000</v>
       </c>
       <c r="E5">
-        <v>44500</v>
+        <f>46500+1000</f>
+        <v>47500</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1024,7 +1021,8 @@
         <v>5000</v>
       </c>
       <c r="E6">
-        <v>48500</v>
+        <f>49500+1000</f>
+        <v>50500</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1053,7 +1051,8 @@
         <v>5000</v>
       </c>
       <c r="E7">
-        <v>122000</v>
+        <f>123000+1000</f>
+        <v>124000</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1082,7 +1081,8 @@
         <v>5000</v>
       </c>
       <c r="E8">
-        <v>46500</v>
+        <f>47500+1000</f>
+        <v>48500</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1111,7 +1111,8 @@
         <v>4000</v>
       </c>
       <c r="E9">
-        <v>111000</v>
+        <f>112000+1000</f>
+        <v>113000</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1140,7 +1141,8 @@
         <v>4000</v>
       </c>
       <c r="E10">
-        <v>46500</v>
+        <f>49500+1000</f>
+        <v>50500</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1169,7 +1171,8 @@
         <v>5000</v>
       </c>
       <c r="E11">
-        <v>103000</v>
+        <f>104000+1000</f>
+        <v>105000</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1198,7 +1201,8 @@
         <v>5000</v>
       </c>
       <c r="E12">
-        <v>46500</v>
+        <f>47500+1000</f>
+        <v>48500</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1227,13 +1231,14 @@
         <v>5000</v>
       </c>
       <c r="E13">
-        <v>120500</v>
+        <f>121500+1000</f>
+        <v>122500</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="H13">
         <v>5825</v>
@@ -1256,7 +1261,8 @@
         <v>4000</v>
       </c>
       <c r="E14">
-        <v>83000</v>
+        <f>84000+1000</f>
+        <v>85000</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1285,7 +1291,8 @@
         <v>5000</v>
       </c>
       <c r="E15">
-        <v>84000</v>
+        <f>85000+1000</f>
+        <v>86000</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1314,7 +1321,8 @@
         <v>4000</v>
       </c>
       <c r="E16">
-        <v>62000</v>
+        <f>67000+1000</f>
+        <v>68000</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1343,7 +1351,8 @@
         <v>3000</v>
       </c>
       <c r="E17">
-        <v>43000</v>
+        <f>44000+1000</f>
+        <v>45000</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1372,7 +1381,8 @@
         <v>3000</v>
       </c>
       <c r="E18">
-        <v>43000</v>
+        <f>44000+1000</f>
+        <v>45000</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1401,7 +1411,8 @@
         <v>3000</v>
       </c>
       <c r="E19">
-        <v>42000</v>
+        <f>43000+1000</f>
+        <v>44000</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1430,7 +1441,8 @@
         <v>1000</v>
       </c>
       <c r="E20">
-        <v>11000</v>
+        <f>41000+1000</f>
+        <v>42000</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1488,7 +1500,8 @@
         <v>3000</v>
       </c>
       <c r="E22">
-        <v>12000</v>
+        <f>48000+1000</f>
+        <v>49000</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1517,7 +1530,8 @@
         <v>3000</v>
       </c>
       <c r="E23">
-        <v>42000</v>
+        <f>43000+1000</f>
+        <v>44000</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1546,7 +1560,8 @@
         <v>3000</v>
       </c>
       <c r="E24">
-        <v>99000</v>
+        <f>100000+1000</f>
+        <v>101000</v>
       </c>
       <c r="F24">
         <v>0</v>

--- a/EGSA2025_performance.xlsx
+++ b/EGSA2025_performance.xlsx
@@ -33,6 +33,9 @@
     <t>monthly_payment</t>
   </si>
   <si>
+    <t>Q2_achievement</t>
+  </si>
+  <si>
     <t>volentary_saving</t>
   </si>
   <si>
@@ -46,9 +49,6 @@
   </si>
   <si>
     <t>NULL</t>
-  </si>
-  <si>
-    <t>achievement</t>
   </si>
 </sst>
 </file>
@@ -872,19 +872,19 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -892,17 +892,16 @@
         <v>1001</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <v>5000</v>
       </c>
       <c r="E2">
-        <f>73000+1000</f>
-        <v>74000</v>
+        <v>73000</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -914,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -922,17 +921,16 @@
         <v>1002</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>17500</v>
+        <v>17750</v>
       </c>
       <c r="D3">
         <v>5000</v>
       </c>
       <c r="E3">
-        <f>133525+1000</f>
-        <v>134525</v>
+        <v>133525</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -961,8 +959,7 @@
         <v>5000</v>
       </c>
       <c r="E4">
-        <f>136500+1000</f>
-        <v>137500</v>
+        <v>136500</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -974,7 +971,7 @@
         <v>15250</v>
       </c>
       <c r="I4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -982,17 +979,16 @@
         <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>3000</v>
       </c>
       <c r="E5">
-        <f>46500+1000</f>
-        <v>47500</v>
+        <v>46500</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1004,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -1021,8 +1017,7 @@
         <v>5000</v>
       </c>
       <c r="E6">
-        <f>49500+1000</f>
-        <v>50500</v>
+        <v>49500</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1034,7 +1029,7 @@
         <v>15250</v>
       </c>
       <c r="I6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1051,8 +1046,7 @@
         <v>5000</v>
       </c>
       <c r="E7">
-        <f>123000+1000</f>
-        <v>124000</v>
+        <v>123000</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1064,7 +1058,7 @@
         <v>15350</v>
       </c>
       <c r="I7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1081,8 +1075,7 @@
         <v>5000</v>
       </c>
       <c r="E8">
-        <f>47500+1000</f>
-        <v>48500</v>
+        <v>47500</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1094,7 +1087,7 @@
         <v>2250</v>
       </c>
       <c r="I8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -1111,8 +1104,7 @@
         <v>4000</v>
       </c>
       <c r="E9">
-        <f>112000+1000</f>
-        <v>113000</v>
+        <v>112000</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1132,17 +1124,16 @@
         <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>4000</v>
       </c>
       <c r="E10">
-        <f>49500+1000</f>
-        <v>50500</v>
+        <v>49500</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1154,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1162,17 +1153,16 @@
         <v>1010</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>7000</v>
+        <v>7250</v>
       </c>
       <c r="D11">
         <v>5000</v>
       </c>
       <c r="E11">
-        <f>104000+1000</f>
-        <v>105000</v>
+        <v>104000</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1184,7 +1174,7 @@
         <v>20250</v>
       </c>
       <c r="I11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1201,8 +1191,7 @@
         <v>5000</v>
       </c>
       <c r="E12">
-        <f>47500+1000</f>
-        <v>48500</v>
+        <v>47500</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1214,7 +1203,7 @@
         <v>2250</v>
       </c>
       <c r="I12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1222,17 +1211,16 @@
         <v>1012</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <v>5000</v>
       </c>
       <c r="E13">
-        <f>121500+1000</f>
-        <v>122500</v>
+        <v>121500</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1261,8 +1249,7 @@
         <v>4000</v>
       </c>
       <c r="E14">
-        <f>84000+1000</f>
-        <v>85000</v>
+        <v>84000</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1274,7 +1261,7 @@
         <v>9250</v>
       </c>
       <c r="I14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1291,8 +1278,7 @@
         <v>5000</v>
       </c>
       <c r="E15">
-        <f>85000+1000</f>
-        <v>86000</v>
+        <v>85000</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1304,7 +1290,7 @@
         <v>2500</v>
       </c>
       <c r="I15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1312,17 +1298,16 @@
         <v>1015</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16">
         <v>4000</v>
       </c>
       <c r="E16">
-        <f>67000+1000</f>
-        <v>68000</v>
+        <v>67000</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1334,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1342,17 +1327,16 @@
         <v>1016</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17">
         <v>3000</v>
       </c>
       <c r="E17">
-        <f>44000+1000</f>
-        <v>45000</v>
+        <v>44000</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1364,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1381,8 +1365,7 @@
         <v>3000</v>
       </c>
       <c r="E18">
-        <f>44000+1000</f>
-        <v>45000</v>
+        <v>44000</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1402,17 +1385,16 @@
         <v>1019</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19">
         <v>3000</v>
       </c>
       <c r="E19">
-        <f>43000+1000</f>
-        <v>44000</v>
+        <v>43000</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1424,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1432,17 +1414,16 @@
         <v>1020</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20">
         <v>1000</v>
       </c>
       <c r="E20">
-        <f>41000+1000</f>
-        <v>42000</v>
+        <v>41000</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1454,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1462,16 +1443,16 @@
         <v>1021</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21">
         <v>2000</v>
       </c>
       <c r="E21">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1483,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1491,17 +1472,16 @@
         <v>1022</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22">
         <v>3000</v>
       </c>
       <c r="E22">
-        <f>48000+1000</f>
-        <v>49000</v>
+        <v>48000</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1513,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -1530,8 +1510,7 @@
         <v>3000</v>
       </c>
       <c r="E23">
-        <f>43000+1000</f>
-        <v>44000</v>
+        <v>43000</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1543,7 +1522,7 @@
         <v>2250</v>
       </c>
       <c r="I23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1551,17 +1530,16 @@
         <v>1024</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24">
         <v>3000</v>
       </c>
       <c r="E24">
-        <f>100000+1000</f>
-        <v>101000</v>
+        <v>100000</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1573,7 +1551,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2025_performance.xlsx
+++ b/EGSA2025_performance.xlsx
@@ -33,9 +33,6 @@
     <t>monthly_payment</t>
   </si>
   <si>
-    <t>Q2_achievement</t>
-  </si>
-  <si>
     <t>volentary_saving</t>
   </si>
   <si>
@@ -49,6 +46,9 @@
   </si>
   <si>
     <t>NULL</t>
+  </si>
+  <si>
+    <t>achievement</t>
   </si>
 </sst>
 </file>
@@ -872,19 +872,19 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -892,10 +892,10 @@
         <v>1001</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>5000</v>
@@ -913,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -971,7 +971,7 @@
         <v>15250</v>
       </c>
       <c r="I4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -979,10 +979,10 @@
         <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>3000</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -1029,7 +1029,7 @@
         <v>15250</v>
       </c>
       <c r="I6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1058,7 +1058,7 @@
         <v>15350</v>
       </c>
       <c r="I7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1087,7 +1087,7 @@
         <v>2250</v>
       </c>
       <c r="I8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -1124,10 +1124,10 @@
         <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <v>4000</v>
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1174,7 +1174,7 @@
         <v>20250</v>
       </c>
       <c r="I11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1203,7 +1203,7 @@
         <v>2250</v>
       </c>
       <c r="I12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1211,10 +1211,10 @@
         <v>1012</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <v>5000</v>
@@ -1261,7 +1261,7 @@
         <v>9250</v>
       </c>
       <c r="I14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1290,7 +1290,7 @@
         <v>2500</v>
       </c>
       <c r="I15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1298,10 +1298,10 @@
         <v>1015</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16">
         <v>4000</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1327,10 +1327,10 @@
         <v>1016</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17">
         <v>3000</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1385,10 +1385,10 @@
         <v>1019</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19">
         <v>3000</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1414,10 +1414,10 @@
         <v>1020</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20">
         <v>1000</v>
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1443,10 +1443,10 @@
         <v>1021</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21">
         <v>2000</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1472,10 +1472,10 @@
         <v>1022</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22">
         <v>3000</v>
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -1522,7 +1522,7 @@
         <v>2250</v>
       </c>
       <c r="I23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1530,10 +1530,10 @@
         <v>1024</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24">
         <v>3000</v>
@@ -1551,7 +1551,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2025_performance.xlsx
+++ b/EGSA2025_performance.xlsx
@@ -857,6 +857,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">

--- a/EGSA2025_performance.xlsx
+++ b/EGSA2025_performance.xlsx
@@ -858,6 +858,9 @@
   <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/EGSA2025_performance.xlsx
+++ b/EGSA2025_performance.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="10">
   <si>
     <t>id</t>
   </si>
@@ -31,6 +31,9 @@
   </si>
   <si>
     <t>monthly_payment</t>
+  </si>
+  <si>
+    <t>Q2_achievement</t>
   </si>
   <si>
     <t>volentary_saving</t>
@@ -46,9 +49,6 @@
   </si>
   <si>
     <t>NULL</t>
-  </si>
-  <si>
-    <t>achievement</t>
   </si>
 </sst>
 </file>
@@ -855,13 +855,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -878,30 +882,30 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3750</v>
       </c>
       <c r="D2">
         <v>5000</v>
@@ -919,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -948,7 +952,7 @@
         <v>23625</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -977,7 +981,7 @@
         <v>15250</v>
       </c>
       <c r="I4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -985,10 +989,10 @@
         <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>3000</v>
@@ -1006,7 +1010,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -1035,7 +1039,7 @@
         <v>15250</v>
       </c>
       <c r="I6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1064,7 +1068,7 @@
         <v>15350</v>
       </c>
       <c r="I7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1093,7 +1097,7 @@
         <v>2250</v>
       </c>
       <c r="I8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -1130,10 +1134,10 @@
         <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>4000</v>
@@ -1151,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1180,7 +1184,7 @@
         <v>20250</v>
       </c>
       <c r="I11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1209,7 +1213,7 @@
         <v>2250</v>
       </c>
       <c r="I12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1217,10 +1221,10 @@
         <v>1012</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <v>5000</v>
@@ -1267,7 +1271,7 @@
         <v>9250</v>
       </c>
       <c r="I14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1296,7 +1300,7 @@
         <v>2500</v>
       </c>
       <c r="I15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1304,10 +1308,10 @@
         <v>1015</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16">
         <v>4000</v>
@@ -1325,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1333,10 +1337,10 @@
         <v>1016</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17">
         <v>3000</v>
@@ -1354,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1362,10 +1366,10 @@
         <v>1017</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>2250</v>
+        <v>6000</v>
       </c>
       <c r="D18">
         <v>3000</v>
@@ -1388,19 +1392,19 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>43000</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1412,24 +1416,24 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="E20">
-        <v>41000</v>
+        <v>43000</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1441,24 +1445,24 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E21">
-        <v>3000</v>
+        <v>41000</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1470,24 +1474,24 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22">
+        <v>2000</v>
+      </c>
+      <c r="E22">
         <v>3000</v>
-      </c>
-      <c r="E22">
-        <v>48000</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1499,24 +1503,24 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>1023</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
-        <v>2250</v>
+        <v>1022</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
       </c>
       <c r="D23">
         <v>3000</v>
       </c>
       <c r="E23">
-        <v>43000</v>
+        <v>48000</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1525,27 +1529,27 @@
         <v>2000</v>
       </c>
       <c r="H23">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>1024</v>
-      </c>
-      <c r="B24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" t="s">
-        <v>8</v>
+        <v>1023</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>2250</v>
       </c>
       <c r="D24">
         <v>3000</v>
       </c>
       <c r="E24">
-        <v>100000</v>
+        <v>43000</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1554,10 +1558,39 @@
         <v>2000</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="I24" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>1024</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25">
+        <v>3000</v>
+      </c>
+      <c r="E25">
+        <v>100000</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>2000</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2025_performance.xlsx
+++ b/EGSA2025_performance.xlsx
@@ -33,9 +33,6 @@
     <t>monthly_payment</t>
   </si>
   <si>
-    <t>Q2_achievement</t>
-  </si>
-  <si>
     <t>volentary_saving</t>
   </si>
   <si>
@@ -49,6 +46,9 @@
   </si>
   <si>
     <t>NULL</t>
+  </si>
+  <si>
+    <t>achievement</t>
   </si>
 </sst>
 </file>
@@ -882,19 +882,19 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -981,7 +981,7 @@
         <v>15250</v>
       </c>
       <c r="I4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -989,10 +989,10 @@
         <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>3000</v>
@@ -1010,7 +1010,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -1039,7 +1039,7 @@
         <v>15250</v>
       </c>
       <c r="I6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1068,7 +1068,7 @@
         <v>15350</v>
       </c>
       <c r="I7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1097,7 +1097,7 @@
         <v>2250</v>
       </c>
       <c r="I8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -1134,10 +1134,10 @@
         <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <v>4000</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1184,7 +1184,7 @@
         <v>20250</v>
       </c>
       <c r="I11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1213,7 +1213,7 @@
         <v>2250</v>
       </c>
       <c r="I12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1221,10 +1221,10 @@
         <v>1012</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <v>5000</v>
@@ -1271,7 +1271,7 @@
         <v>9250</v>
       </c>
       <c r="I14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1300,7 +1300,7 @@
         <v>2500</v>
       </c>
       <c r="I15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1308,10 +1308,10 @@
         <v>1015</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16">
         <v>4000</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1337,10 +1337,10 @@
         <v>1016</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17">
         <v>3000</v>
@@ -1358,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1395,10 +1395,10 @@
         <v>1018</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1424,10 +1424,10 @@
         <v>1019</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20">
         <v>3000</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1453,10 +1453,10 @@
         <v>1020</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21">
         <v>1000</v>
@@ -1474,7 +1474,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1482,10 +1482,10 @@
         <v>1021</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22">
         <v>2000</v>
@@ -1503,7 +1503,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -1511,10 +1511,10 @@
         <v>1022</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23">
         <v>3000</v>
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1561,7 +1561,7 @@
         <v>2250</v>
       </c>
       <c r="I24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -1569,10 +1569,10 @@
         <v>1024</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25">
         <v>3000</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2025_performance.xlsx
+++ b/EGSA2025_performance.xlsx
@@ -33,6 +33,9 @@
     <t>monthly_payment</t>
   </si>
   <si>
+    <t>Q2_achievement</t>
+  </si>
+  <si>
     <t>volentary_saving</t>
   </si>
   <si>
@@ -46,9 +49,6 @@
   </si>
   <si>
     <t>NULL</t>
-  </si>
-  <si>
-    <t>achievement</t>
   </si>
 </sst>
 </file>
@@ -882,19 +882,19 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -931,10 +931,10 @@
         <v>1002</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>17750</v>
+        <v>19250</v>
       </c>
       <c r="D3">
         <v>5000</v>
@@ -981,7 +981,7 @@
         <v>15250</v>
       </c>
       <c r="I4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -989,10 +989,10 @@
         <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>3000</v>
@@ -1010,7 +1010,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -1039,7 +1039,7 @@
         <v>15250</v>
       </c>
       <c r="I6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1068,7 +1068,7 @@
         <v>15350</v>
       </c>
       <c r="I7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1097,7 +1097,7 @@
         <v>2250</v>
       </c>
       <c r="I8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -1134,10 +1134,10 @@
         <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>4000</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1184,7 +1184,7 @@
         <v>20250</v>
       </c>
       <c r="I11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1213,7 +1213,7 @@
         <v>2250</v>
       </c>
       <c r="I12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1221,10 +1221,10 @@
         <v>1012</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <v>5000</v>
@@ -1271,7 +1271,7 @@
         <v>9250</v>
       </c>
       <c r="I14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1300,7 +1300,7 @@
         <v>2500</v>
       </c>
       <c r="I15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1308,10 +1308,10 @@
         <v>1015</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16">
         <v>4000</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1337,10 +1337,10 @@
         <v>1016</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17">
         <v>3000</v>
@@ -1358,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1395,10 +1395,10 @@
         <v>1018</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1424,10 +1424,10 @@
         <v>1019</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20">
         <v>3000</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1453,10 +1453,10 @@
         <v>1020</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21">
         <v>1000</v>
@@ -1474,7 +1474,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1482,10 +1482,10 @@
         <v>1021</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22">
         <v>2000</v>
@@ -1503,7 +1503,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -1511,10 +1511,10 @@
         <v>1022</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23">
         <v>3000</v>
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1561,7 +1561,7 @@
         <v>2250</v>
       </c>
       <c r="I24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -1569,10 +1569,10 @@
         <v>1024</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25">
         <v>3000</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2025_performance.xlsx
+++ b/EGSA2025_performance.xlsx
@@ -33,6 +33,9 @@
     <t>monthly_payment</t>
   </si>
   <si>
+    <t>achievement</t>
+  </si>
+  <si>
     <t>volentary_saving</t>
   </si>
   <si>
@@ -46,9 +49,6 @@
   </si>
   <si>
     <t>NULL</t>
-  </si>
-  <si>
-    <t>achievement</t>
   </si>
 </sst>
 </file>
@@ -858,14 +858,7 @@
   <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -882,19 +875,19 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -923,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -981,7 +974,7 @@
         <v>15250</v>
       </c>
       <c r="I4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -989,10 +982,10 @@
         <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>3000</v>
@@ -1010,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -1039,7 +1032,7 @@
         <v>15250</v>
       </c>
       <c r="I6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1068,7 +1061,7 @@
         <v>15350</v>
       </c>
       <c r="I7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1097,7 +1090,7 @@
         <v>2250</v>
       </c>
       <c r="I8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -1134,10 +1127,10 @@
         <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>4000</v>
@@ -1155,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1184,7 +1177,7 @@
         <v>20250</v>
       </c>
       <c r="I11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1213,7 +1206,7 @@
         <v>2250</v>
       </c>
       <c r="I12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1221,10 +1214,10 @@
         <v>1012</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <v>5000</v>
@@ -1271,7 +1264,7 @@
         <v>9250</v>
       </c>
       <c r="I14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1300,7 +1293,7 @@
         <v>2500</v>
       </c>
       <c r="I15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1308,10 +1301,10 @@
         <v>1015</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16">
         <v>4000</v>
@@ -1329,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1337,10 +1330,10 @@
         <v>1016</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17">
         <v>3000</v>
@@ -1358,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1395,10 +1388,10 @@
         <v>1018</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1416,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1424,10 +1417,10 @@
         <v>1019</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20">
         <v>3000</v>
@@ -1445,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1453,10 +1446,10 @@
         <v>1020</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21">
         <v>1000</v>
@@ -1474,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1482,10 +1475,10 @@
         <v>1021</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22">
         <v>2000</v>
@@ -1503,7 +1496,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -1511,10 +1504,10 @@
         <v>1022</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23">
         <v>3000</v>
@@ -1532,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1561,7 +1554,7 @@
         <v>2250</v>
       </c>
       <c r="I24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -1569,10 +1562,10 @@
         <v>1024</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25">
         <v>3000</v>
@@ -1590,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2025_performance.xlsx
+++ b/EGSA2025_performance.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="10">
   <si>
     <t>id</t>
   </si>
@@ -855,11 +855,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -901,10 +898,10 @@
         <v>3750</v>
       </c>
       <c r="D2">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="E2">
-        <v>73000</v>
+        <v>75000</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -930,22 +927,22 @@
         <v>19250</v>
       </c>
       <c r="D3">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="E3">
-        <v>133525</v>
+        <v>150000</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1400</v>
+        <v>1900</v>
       </c>
       <c r="H3">
-        <v>23625</v>
+        <v>24125</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -959,19 +956,19 @@
         <v>17250</v>
       </c>
       <c r="D4">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="E4">
-        <v>136500</v>
+        <v>150000</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>650</v>
+        <v>1150</v>
       </c>
       <c r="H4">
-        <v>15250</v>
+        <v>16250</v>
       </c>
       <c r="I4" t="s">
         <v>9</v>
@@ -988,10 +985,10 @@
         <v>9</v>
       </c>
       <c r="D5">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E5">
-        <v>46500</v>
+        <v>48500</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1017,10 +1014,10 @@
         <v>6000</v>
       </c>
       <c r="D6">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="E6">
-        <v>49500</v>
+        <v>51500</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1046,10 +1043,10 @@
         <v>17350</v>
       </c>
       <c r="D7">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="E7">
-        <v>123000</v>
+        <v>125000</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1075,10 +1072,10 @@
         <v>6000</v>
       </c>
       <c r="D8">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="E8">
-        <v>47500</v>
+        <v>49500</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1098,16 +1095,16 @@
         <v>1008</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>2250</v>
+        <v>17250</v>
       </c>
       <c r="D9">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="E9">
-        <v>112000</v>
+        <v>123000</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1136,7 +1133,7 @@
         <v>4000</v>
       </c>
       <c r="E10">
-        <v>49500</v>
+        <v>50500</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1156,25 +1153,25 @@
         <v>1010</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11">
-        <v>7250</v>
+        <v>7750</v>
       </c>
       <c r="D11">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="E11">
-        <v>104000</v>
+        <v>106000</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>4400</v>
+        <v>5100</v>
       </c>
       <c r="H11">
-        <v>20250</v>
+        <v>22625</v>
       </c>
       <c r="I11" t="s">
         <v>9</v>
@@ -1185,16 +1182,16 @@
         <v>1011</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12">
+        <v>9750</v>
+      </c>
+      <c r="D12">
         <v>6000</v>
       </c>
-      <c r="D12">
-        <v>5000</v>
-      </c>
       <c r="E12">
-        <v>47500</v>
+        <v>49500</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1220,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="D13">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="E13">
-        <v>121500</v>
+        <v>123500</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1249,10 +1246,10 @@
         <v>2250</v>
       </c>
       <c r="D14">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="E14">
-        <v>84000</v>
+        <v>86000</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1278,10 +1275,10 @@
         <v>2500</v>
       </c>
       <c r="D15">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="E15">
-        <v>85000</v>
+        <v>87000</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1307,10 +1304,10 @@
         <v>9</v>
       </c>
       <c r="D16">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="E16">
-        <v>67000</v>
+        <v>73000</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1339,7 +1336,7 @@
         <v>3000</v>
       </c>
       <c r="E17">
-        <v>44000</v>
+        <v>45000</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1365,10 +1362,10 @@
         <v>6000</v>
       </c>
       <c r="D18">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E18">
-        <v>44000</v>
+        <v>46000</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1394,10 +1391,10 @@
         <v>9</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1426,7 +1423,7 @@
         <v>3000</v>
       </c>
       <c r="E20">
-        <v>43000</v>
+        <v>44000</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1452,10 +1449,10 @@
         <v>9</v>
       </c>
       <c r="D21">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E21">
-        <v>41000</v>
+        <v>43000</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1484,7 +1481,7 @@
         <v>2000</v>
       </c>
       <c r="E22">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1510,10 +1507,10 @@
         <v>9</v>
       </c>
       <c r="D23">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E23">
-        <v>48000</v>
+        <v>50000</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1539,10 +1536,10 @@
         <v>2250</v>
       </c>
       <c r="D24">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E24">
-        <v>43000</v>
+        <v>45000</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1571,7 +1568,7 @@
         <v>3000</v>
       </c>
       <c r="E25">
-        <v>100000</v>
+        <v>101000</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1583,6 +1580,64 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>1025</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26">
+        <v>1000</v>
+      </c>
+      <c r="E26">
+        <v>41000</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>2500</v>
+      </c>
+      <c r="H26">
+        <v>500</v>
+      </c>
+      <c r="I26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>1026</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27">
+        <v>1000</v>
+      </c>
+      <c r="E27">
+        <v>43000</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>2000</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" t="s">
         <v>9</v>
       </c>
     </row>

--- a/EGSA2025_performance.xlsx
+++ b/EGSA2025_performance.xlsx
@@ -857,6 +857,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1046,16 +1056,16 @@
         <v>6000</v>
       </c>
       <c r="E7">
-        <v>125000</v>
+        <v>150000</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>650</v>
+        <v>1650</v>
       </c>
       <c r="H7">
-        <v>15350</v>
+        <v>16350</v>
       </c>
       <c r="I7" t="s">
         <v>9</v>
@@ -1110,7 +1120,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>650</v>
+        <v>1650</v>
       </c>
       <c r="H9">
         <v>15250</v>
@@ -1153,16 +1163,16 @@
         <v>1010</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>7750</v>
+        <v>22750</v>
       </c>
       <c r="D11">
         <v>6000</v>
       </c>
       <c r="E11">
-        <v>106000</v>
+        <v>121500</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1420,10 +1430,10 @@
         <v>9</v>
       </c>
       <c r="D20">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1432,7 +1442,7 @@
         <v>2000</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="I20" t="s">
         <v>9</v>

--- a/EGSA2025_performance.xlsx
+++ b/EGSA2025_performance.xlsx
@@ -857,16 +857,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.21875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -931,10 +921,10 @@
         <v>1002</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>19250</v>
+        <v>20750</v>
       </c>
       <c r="D3">
         <v>6000</v>
@@ -998,16 +988,16 @@
         <v>4000</v>
       </c>
       <c r="E5">
-        <v>48500</v>
+        <v>73000</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I5" t="s">
         <v>9</v>
@@ -1018,10 +1008,10 @@
         <v>1005</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>6000</v>
+        <v>9750</v>
       </c>
       <c r="D6">
         <v>6000</v>
@@ -1076,10 +1066,10 @@
         <v>1007</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>6000</v>
+        <v>9750</v>
       </c>
       <c r="D8">
         <v>6000</v>
@@ -1143,7 +1133,7 @@
         <v>4000</v>
       </c>
       <c r="E10">
-        <v>50500</v>
+        <v>53500</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1163,25 +1153,25 @@
         <v>1010</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>22750</v>
+        <v>24250</v>
       </c>
       <c r="D11">
         <v>6000</v>
       </c>
       <c r="E11">
-        <v>121500</v>
+        <v>150000</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>5100</v>
+        <v>6100</v>
       </c>
       <c r="H11">
-        <v>22625</v>
+        <v>23625</v>
       </c>
       <c r="I11" t="s">
         <v>9</v>
@@ -1297,7 +1287,7 @@
         <v>1250</v>
       </c>
       <c r="H15">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="I15" t="s">
         <v>9</v>
@@ -1375,7 +1365,7 @@
         <v>4000</v>
       </c>
       <c r="E18">
-        <v>46000</v>
+        <v>55600</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1404,7 +1394,7 @@
         <v>1000</v>
       </c>
       <c r="E19">
-        <v>1000</v>
+        <v>41000</v>
       </c>
       <c r="F19">
         <v>0</v>
